--- a/data/harmonized_windsor_detroit_monthly.xlsx
+++ b/data/harmonized_windsor_detroit_monthly.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Windsor-Detroit" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sarnia-Port Huron (BWB)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Windsor-Detroit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sarnia-Port Huron (BWB)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Methodology" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2087,7 +2087,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-11 19:48 UTC</t>
+          <t>Rebuilt: 2026-09-11 19:51 UTC</t>
         </is>
       </c>
     </row>

--- a/data/harmonized_windsor_detroit_monthly.xlsx
+++ b/data/harmonized_windsor_detroit_monthly.xlsx
@@ -2087,7 +2087,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-11 19:51 UTC</t>
+          <t>Rebuilt: 2026-09-11 19:59 UTC</t>
         </is>
       </c>
     </row>

--- a/data/harmonized_windsor_detroit_monthly.xlsx
+++ b/data/harmonized_windsor_detroit_monthly.xlsx
@@ -2087,7 +2087,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-11 19:59 UTC</t>
+          <t>Rebuilt: 2026-09-11 20:09 UTC</t>
         </is>
       </c>
     </row>

--- a/data/harmonized_windsor_detroit_monthly.xlsx
+++ b/data/harmonized_windsor_detroit_monthly.xlsx
@@ -1211,11 +1211,21 @@
       <c r="B33" t="n">
         <v>592286</v>
       </c>
+      <c r="C33" t="n">
+        <v>691475</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1283761</v>
+      </c>
       <c r="E33" s="2" t="n">
         <v>0.08355439121573907</v>
       </c>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
+      <c r="F33" s="2" t="n">
+        <v>0.1169847590278731</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0.1013083473953584</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2005,11 +2015,21 @@
       <c r="B33" t="n">
         <v>188667</v>
       </c>
+      <c r="C33" t="n">
+        <v>226354</v>
+      </c>
+      <c r="D33" t="n">
+        <v>415021</v>
+      </c>
       <c r="E33" s="2" t="n">
         <v>0.004835986557235605</v>
       </c>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
+      <c r="F33" s="2" t="n">
+        <v>0.08016511178449572</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0.04456676583256568</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2087,7 +2107,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-11 20:09 UTC</t>
+          <t>Rebuilt: 2026-09-22 17:24 UTC</t>
         </is>
       </c>
     </row>

--- a/data/harmonized_windsor_detroit_monthly.xlsx
+++ b/data/harmonized_windsor_detroit_monthly.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -574,9 +574,7 @@
       <c r="D6" t="n">
         <v>1051561</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>1.532513977995929</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
     </row>
@@ -596,7 +594,7 @@
         <v>1035499</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.1018439657856659</v>
+        <v>1.67281471978318</v>
       </c>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
@@ -1226,6 +1224,21 @@
       <c r="G33" s="2" t="n">
         <v>0.1013083473953584</v>
       </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>461549</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0.09570689925314671</v>
+      </c>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1238,7 +1251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1378,9 +1391,7 @@
       <c r="D6" t="n">
         <v>372241</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>1.354302299263756</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
     </row>
@@ -1400,7 +1411,7 @@
         <v>390742</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.01982655809008834</v>
+        <v>1.446324319426286</v>
       </c>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
@@ -2030,6 +2041,21 @@
       <c r="G33" s="2" t="n">
         <v>0.04456676583256568</v>
       </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>136619</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0.1880429583894952</v>
+      </c>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2107,7 +2133,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-22 17:24 UTC</t>
+          <t>Rebuilt: 2026-10-13 19:51 UTC</t>
         </is>
       </c>
     </row>

--- a/data/harmonized_windsor_detroit_monthly.xlsx
+++ b/data/harmonized_windsor_detroit_monthly.xlsx
@@ -1234,11 +1234,21 @@
       <c r="B34" t="n">
         <v>461549</v>
       </c>
+      <c r="C34" t="n">
+        <v>539103</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1000652</v>
+      </c>
       <c r="E34" s="2" t="n">
         <v>0.09570689925314671</v>
       </c>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
+      <c r="F34" s="2" t="n">
+        <v>0.1105290587849961</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0.1036428468226421</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2051,11 +2061,21 @@
       <c r="B34" t="n">
         <v>136619</v>
       </c>
+      <c r="C34" t="n">
+        <v>160284</v>
+      </c>
+      <c r="D34" t="n">
+        <v>296903</v>
+      </c>
       <c r="E34" s="2" t="n">
         <v>0.1880429583894952</v>
       </c>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
+      <c r="F34" s="2" t="n">
+        <v>0.1619834710743802</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0.1738312214600589</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2133,7 +2153,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-10-13 19:51 UTC</t>
+          <t>Rebuilt: 2026-10-20 17:36 UTC</t>
         </is>
       </c>
     </row>
